--- a/data/output/2025/evaluasi_14.xlsx
+++ b/data/output/2025/evaluasi_14.xlsx
@@ -15,6 +15,11 @@
     <sheet name="1408" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="1409" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="1473" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1407" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1410" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1471" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="1401" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="1402" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -836,6 +841,778 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Meranti</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.7169805720601624</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Meranti</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>15.95168266472506</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Meranti</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.851324539999974</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Meranti</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.776809697403953</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Meranti</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.923537526938448</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.443254350051059</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>18.96225320172677</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.101424537004916</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.879441454312857</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.79895706862578</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.378768297069864</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuantan Singingi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.09476746477705</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuantan Singingi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>23.50179096701999</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuantan Singingi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.886636305857826</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuantan Singingi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.014906528966653</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Indragiri Hulu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.294408120568155</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Indragiri Hulu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20.49384235181288</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Indragiri Hulu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.278599026963879</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Indragiri Hulu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2804854111796607</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Indragiri Hulu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.437570516139359</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Indragiri Hulu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.8493646890434128</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -916,7 +1693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +1753,90 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pelalawan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.396293905619891</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pelalawan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.4599269130706524</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pelalawan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.094252179999994</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -990,7 +1851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1050,6 +1911,62 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Siak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.346394557560825</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Siak</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.03348156217999795</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +2041,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kampar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.179344833097732</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kampar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.558591593105786</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kampar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>29.72418558175936</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kampar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.416725172496977</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kampar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1348826293519712</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1138,7 +2195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,6 +2255,34 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkalis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.276452949249232</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1212,7 +2297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1272,6 +2357,62 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1409</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Rokan Hilir</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.905824704220178</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1409</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Rokan Hilir</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1357271717288563</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1286,7 +2427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1349,6 +2490,332 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Dumai</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.1041351542642</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Dumai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16.78928632024152</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Dumai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-8.49808889147625</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Dumai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.299629209431195</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Dumai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.8937903575425097</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Rokan Hulu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.7391246321195165</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Rokan Hulu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>22.87060828786255</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Rokan Hulu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-9.416200056865799</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Rokan Hulu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.029999999999839</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Rokan Hulu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01933679645508436</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
